--- a/data/trans_orig/P21D1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D1_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención médica en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención médica en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49956</t>
+          <t>50635</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97595</t>
+          <t>94882</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27463</t>
+          <t>30044</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59931</t>
+          <t>61952</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88638</t>
+          <t>88607</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141913</t>
+          <t>144777</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>42,05%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99862</t>
+          <t>102969</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146818</t>
+          <t>148915</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78118</t>
+          <t>77986</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>109684</t>
+          <t>108886</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>193262</t>
+          <t>190916</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>247351</t>
+          <t>246992</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,74%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23071</t>
+          <t>21280</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>11381</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25132</t>
+          <t>25968</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4544</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2861</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3690</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61805</t>
+          <t>64255</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>97287</t>
+          <t>100228</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57401</t>
+          <t>55745</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>213108</t>
+          <t>210683</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>142964</t>
+          <t>140515</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>314806</t>
+          <t>304410</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>61,39%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>104056</t>
+          <t>101843</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>139900</t>
+          <t>137242</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75595</t>
+          <t>77156</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>226526</t>
+          <t>228309</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>173963</t>
+          <t>184858</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>342272</t>
+          <t>346053</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,79%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8824</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13555</t>
+          <t>14943</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17764</t>
+          <t>18231</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -1638,97 +1638,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2689</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2545</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45411</t>
+          <t>45713</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74205</t>
+          <t>73025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49616</t>
+          <t>49486</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72174</t>
+          <t>72391</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>100568</t>
+          <t>102203</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>138886</t>
+          <t>139666</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>136834</t>
+          <t>137836</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>166246</t>
+          <t>164845</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177414</t>
+          <t>177974</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>201271</t>
+          <t>201695</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>322520</t>
+          <t>322290</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>360295</t>
+          <t>359429</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,96%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15227</t>
+          <t>13014</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12308</t>
+          <t>12542</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20860</t>
+          <t>20834</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -2207,97 +2207,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1854</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3836</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3849</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>3635</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>3580</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23534</t>
+          <t>23086</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>143003</t>
+          <t>143776</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52252</t>
+          <t>52193</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>75536</t>
+          <t>77116</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59843</t>
+          <t>62609</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>200233</t>
+          <t>198686</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>373374</t>
+          <t>372533</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>501484</t>
+          <t>502848</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>238953</t>
+          <t>238799</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>263367</t>
+          <t>263697</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>632232</t>
+          <t>634751</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>781668</t>
+          <t>778946</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>91,9%</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15146</t>
+          <t>14779</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9932</t>
+          <t>10944</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20276</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -2776,97 +2776,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3403</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>1163</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29376</t>
+          <t>28855</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>51742</t>
+          <t>51226</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21765</t>
+          <t>21219</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>36049</t>
+          <t>36388</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>55985</t>
+          <t>56346</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>82565</t>
+          <t>83177</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>180244</t>
+          <t>180138</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>203895</t>
+          <t>203735</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>185929</t>
+          <t>184939</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>201385</t>
+          <t>200998</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>369871</t>
+          <t>369852</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>398582</t>
+          <t>398136</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,47%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13849</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8485</t>
+          <t>8676</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>5856</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17764</t>
+          <t>18228</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -3345,97 +3345,97 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1641</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2966</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="S27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>3789</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>3452</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14823</t>
+          <t>14600</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28437</t>
+          <t>27761</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14567</t>
+          <t>14276</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>26335</t>
+          <t>26185</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31768</t>
+          <t>32238</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>49976</t>
+          <t>50218</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>125094</t>
+          <t>125139</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>139551</t>
+          <t>139415</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>154252</t>
+          <t>155303</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>167246</t>
+          <t>168201</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>285212</t>
+          <t>284592</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>304693</t>
+          <t>304793</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>780</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>6682</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7707</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3412</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11873</t>
+          <t>11585</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -3914,97 +3914,97 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1235</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>949</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>16347</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7758</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>18916</t>
+          <t>19487</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>15879</t>
+          <t>17135</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>31137</t>
+          <t>31406</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>101398</t>
+          <t>101859</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>111929</t>
+          <t>111933</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>149630</t>
+          <t>149437</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>161083</t>
+          <t>160391</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>255383</t>
+          <t>255463</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>271221</t>
+          <t>270106</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>699</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>529</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -4483,97 +4483,97 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>1175</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>1031</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>219253</t>
+          <t>215490</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>433588</t>
+          <t>430323</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>276550</t>
+          <t>277201</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>535091</t>
+          <t>535322</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>566544</t>
+          <t>569493</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>871893</t>
+          <t>879865</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1199514</t>
+          <t>1200333</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1435166</t>
+          <t>1422602</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1027660</t>
+          <t>1032877</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1283586</t>
+          <t>1283367</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2331560</t>
+          <t>2317847</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2642692</t>
+          <t>2635653</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>80,9%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>15263</t>
+          <t>15095</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>45098</t>
+          <t>45395</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>22945</t>
+          <t>22932</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>42813</t>
+          <t>45318</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>42308</t>
+          <t>43302</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>81024</t>
+          <t>79425</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -5052,97 +5052,97 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>2187</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>4426</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="R42" s="2" t="inlineStr">
         <is>
           <t>1400</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="S42" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>4422</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>5358</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>0,04%</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>5380</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D1_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>72618</t>
+          <t>89103</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50635</t>
+          <t>65297</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94882</t>
+          <t>112010</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42638</t>
+          <t>50986</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30044</t>
+          <t>35345</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61952</t>
+          <t>68475</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>115255</t>
+          <t>140089</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88607</t>
+          <t>115265</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144777</t>
+          <t>170560</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>45,63%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>125399</t>
+          <t>114817</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102969</t>
+          <t>91564</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>148915</t>
+          <t>139061</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>94386</t>
+          <t>108352</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77986</t>
+          <t>90296</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>108886</t>
+          <t>123689</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>219784</t>
+          <t>223169</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>190916</t>
+          <t>190628</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>246992</t>
+          <t>247959</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>66,34%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>25859</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11381</t>
+          <t>12060</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>10509</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25968</t>
+          <t>25543</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>81765</t>
+          <t>93053</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64255</t>
+          <t>73624</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100228</t>
+          <t>112724</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>116652</t>
+          <t>53859</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55745</t>
+          <t>41551</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>210683</t>
+          <t>69431</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>198417</t>
+          <t>146912</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>140515</t>
+          <t>123543</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>304410</t>
+          <t>173606</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>120321</t>
+          <t>131196</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>101843</t>
+          <t>111666</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>137242</t>
+          <t>150551</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>168652</t>
+          <t>190366</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77156</t>
+          <t>173922</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>228309</t>
+          <t>204042</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>288973</t>
+          <t>321562</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>184858</t>
+          <t>294252</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>346053</t>
+          <t>344553</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>72,21%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14943</t>
+          <t>14222</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,27 +1590,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>8692</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18231</t>
+          <t>17581</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>57719</t>
+          <t>75420</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45713</t>
+          <t>61212</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73025</t>
+          <t>91890</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>60462</t>
+          <t>68633</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49486</t>
+          <t>56411</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72391</t>
+          <t>82109</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>118182</t>
+          <t>144053</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>102203</t>
+          <t>124171</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>139666</t>
+          <t>165887</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>30,21%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>152238</t>
+          <t>170067</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>137836</t>
+          <t>154885</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>164845</t>
+          <t>185514</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>189936</t>
+          <t>220282</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177974</t>
+          <t>206575</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>201695</t>
+          <t>233500</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>342174</t>
+          <t>390349</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>322290</t>
+          <t>368670</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>359429</t>
+          <t>411624</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>74,96%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>7031</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13014</t>
+          <t>15316</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,59 +2124,59 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6578</t>
+          <t>6972</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12542</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>14003</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>24357</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>2,55%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>12106</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>6315</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>20834</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
           <t>1,33%</t>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>749</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>749</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>72027</t>
+          <t>79671</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23086</t>
+          <t>64316</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>143776</t>
+          <t>95488</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>63059</t>
+          <t>70179</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52193</t>
+          <t>58434</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77116</t>
+          <t>83050</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>135085</t>
+          <t>149850</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>62609</t>
+          <t>128122</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>198686</t>
+          <t>169643</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>449439</t>
+          <t>232048</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>372533</t>
+          <t>214876</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>502848</t>
+          <t>247058</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>252205</t>
+          <t>269874</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>238799</t>
+          <t>256858</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>263697</t>
+          <t>281923</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>701644</t>
+          <t>501922</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>634751</t>
+          <t>481103</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>778946</t>
+          <t>524301</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>79,02%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14779</t>
+          <t>13006</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5756</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10944</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>10848</t>
+          <t>11754</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20276</t>
+          <t>20975</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>321020</t>
+          <t>346458</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>321020</t>
+          <t>346458</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>321020</t>
+          <t>346458</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>847578</t>
+          <t>663526</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>847578</t>
+          <t>663526</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>847578</t>
+          <t>663526</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>39617</t>
+          <t>45738</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28855</t>
+          <t>34945</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>51226</t>
+          <t>59978</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28723</t>
+          <t>33403</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21219</t>
+          <t>26022</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>36388</t>
+          <t>42094</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>68340</t>
+          <t>79141</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>56346</t>
+          <t>65531</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>83177</t>
+          <t>95020</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>192798</t>
+          <t>205662</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>180138</t>
+          <t>191689</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>203735</t>
+          <t>217908</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>193520</t>
+          <t>215380</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>184939</t>
+          <t>205988</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>200998</t>
+          <t>223062</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>386318</t>
+          <t>421042</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>369852</t>
+          <t>404977</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>398136</t>
+          <t>435957</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>6081</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13114</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>10772</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18228</t>
+          <t>18151</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3385,12 +3385,12 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>465830</t>
+          <t>511657</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>465830</t>
+          <t>511657</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>465830</t>
+          <t>511657</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>21004</t>
+          <t>24202</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>16998</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27761</t>
+          <t>32485</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>19519</t>
+          <t>21068</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14276</t>
+          <t>15821</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>26185</t>
+          <t>28352</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>40523</t>
+          <t>45270</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32238</t>
+          <t>35813</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>50218</t>
+          <t>56001</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>132886</t>
+          <t>146918</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>125139</t>
+          <t>137647</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>139415</t>
+          <t>154438</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>162298</t>
+          <t>174254</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>155303</t>
+          <t>167163</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>168201</t>
+          <t>180136</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>295183</t>
+          <t>321172</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>284592</t>
+          <t>309933</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>304793</t>
+          <t>331006</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,59%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2933</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>907</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7707</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3473</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11585</t>
+          <t>12739</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>185860</t>
+          <t>199573</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>185860</t>
+          <t>199573</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>185860</t>
+          <t>199573</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>342213</t>
+          <t>373626</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>342213</t>
+          <t>373626</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>342213</t>
+          <t>373626</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>12243</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16347</t>
+          <t>19740</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>13071</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>9556</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>19487</t>
+          <t>22009</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>23465</t>
+          <t>27080</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>17135</t>
+          <t>19824</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>31406</t>
+          <t>36531</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>107812</t>
+          <t>117318</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>101859</t>
+          <t>109821</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>111933</t>
+          <t>121956</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>155608</t>
+          <t>169920</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>149437</t>
+          <t>162520</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>160391</t>
+          <t>175504</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>263420</t>
+          <t>287238</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>255463</t>
+          <t>277730</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>270106</t>
+          <t>294326</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,05%</t>
         </is>
       </c>
     </row>
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>568</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,22 +4435,22 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>583</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>170615</t>
+          <t>186755</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>170615</t>
+          <t>186755</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>170615</t>
+          <t>186755</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>288822</t>
+          <t>316316</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>288822</t>
+          <t>316316</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>288822</t>
+          <t>316316</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>355145</t>
+          <t>419429</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>215490</t>
+          <t>379801</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>430323</t>
+          <t>462742</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>344124</t>
+          <t>312965</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>277201</t>
+          <t>287162</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>535322</t>
+          <t>344682</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>699268</t>
+          <t>732394</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>569493</t>
+          <t>680259</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>879865</t>
+          <t>785874</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1280892</t>
+          <t>1118025</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1200333</t>
+          <t>1073216</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1422602</t>
+          <t>1157753</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1216604</t>
+          <t>1348428</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1032877</t>
+          <t>1316039</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1283367</t>
+          <t>1377198</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>2497496</t>
+          <t>2466454</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2317847</t>
+          <t>2414253</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2635653</t>
+          <t>2517654</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>77,11%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>27741</t>
+          <t>30819</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>15095</t>
+          <t>18681</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>45395</t>
+          <t>49705</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>31847</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>22932</t>
+          <t>24649</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>45318</t>
+          <t>46802</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>59588</t>
+          <t>64911</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>43302</t>
+          <t>50519</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>79425</t>
+          <t>86728</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
